--- a/Sheets/AnimationData.xlsx
+++ b/Sheets/AnimationData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9135353C-178F-4BA1-B701-DE394DAFD7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D37881-C49C-4A31-BA68-7070D66562BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="106">
   <si>
     <t>$$AnimationData_Player$$</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -403,6 +403,10 @@
   </si>
   <si>
     <t>24-27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MiniVillagerWoman_sleep</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2571,11 +2575,24 @@
       <c r="Q9" s="6"/>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
+      <c r="A10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" s="6">
+        <v>30</v>
+      </c>
+      <c r="F10" s="6" t="b">
+        <v>1</v>
+      </c>
       <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
     </row>
